--- a/Солиштирма далолатномалар.xlsx
+++ b/Солиштирма далолатномалар.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8616"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8616" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Нурли замин" sheetId="1" r:id="rId1"/>
@@ -106,9 +106,6 @@
     <t>Н. Холбаев</t>
   </si>
   <si>
-    <t>Натижада: 2026 йил 01 Сентябрь холатига "NAM PAXTA TEKS GALLA" MCHJ" (тўқсон тўрт миллион тўрт юз ўн бир минг бир юз саксон тўққиз) хақдор эканлиги аниқланди.</t>
-  </si>
-  <si>
     <t>Уйчи тумани, Гулистон қишлоғи</t>
   </si>
   <si>
@@ -116,6 +113,9 @@
   </si>
   <si>
     <t>Бизлар ким қуйида имзо чекиб далолатнома тузувчилар "NAM PAXTA TEKS GALLA" MCHJ" МЧЖ рахбари Ё.Жамолитдинов ва "BIRLASHGAN NURLI ZAMIN" FX рахбари З. Рахимовлар бўлиб тузамиз ушбу далолатномани шу хақдаки, ташкилотларимиз ўртасидаги ўзаро молиявий алоқаларни 2026 йил 1 сентябрь холатига солиштириб кўрганимизда қуйидагилар аниқланди.</t>
+  </si>
+  <si>
+    <t>Натижада: 2026 йил 01 Сентябрь холатига "NAM PAXTA TEKS GALLA" MCHJ" (тўқсон тўрт миллион тўрт юз қирқ бир минг бир юз саксон тўққиз) хақдор эканлиги аниқланди.</t>
   </si>
 </sst>
 </file>
@@ -272,6 +272,18 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -288,18 +300,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -600,52 +600,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="3" spans="2:8" ht="18" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="20"/>
+      <c r="G3" s="14"/>
     </row>
     <row r="5" spans="2:8" ht="141.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
+      <c r="B5" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
     </row>
     <row r="7" spans="2:8" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22" t="s">
+      <c r="E7" s="16"/>
+      <c r="F7" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="22"/>
+      <c r="G7" s="16"/>
     </row>
     <row r="8" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
       <c r="D8" s="3" t="s">
         <v>4</v>
       </c>
@@ -690,38 +690,38 @@
       <c r="G10" s="7"/>
     </row>
     <row r="12" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
     </row>
     <row r="14" spans="2:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C14" s="15" t="str">
+      <c r="C14" s="19" t="str">
         <f>+D7</f>
         <v>""NAM PAXTA TEKS GALLA" MCHJ"</v>
       </c>
-      <c r="D14" s="15"/>
+      <c r="D14" s="19"/>
       <c r="E14" s="8"/>
-      <c r="F14" s="16" t="str">
+      <c r="F14" s="20" t="str">
         <f>+F7</f>
         <v>"BIRLASHGAN NURLI ZAMIN" FX</v>
       </c>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
     </row>
     <row r="15" spans="2:8" ht="59.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="17"/>
+      <c r="D15" s="21"/>
       <c r="E15" s="8"/>
-      <c r="F15" s="18" t="s">
+      <c r="F15" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="G15" s="18"/>
+      <c r="G15" s="22"/>
       <c r="H15" s="9"/>
     </row>
     <row r="16" spans="2:8" ht="21" x14ac:dyDescent="0.4">
@@ -783,10 +783,10 @@
       <c r="F20" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="G20" s="13" t="s">
+      <c r="G20" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="H20" s="13"/>
+      <c r="H20" s="17"/>
     </row>
     <row r="21" spans="3:8" ht="21" x14ac:dyDescent="0.4">
       <c r="C21" s="8"/>
@@ -805,8 +805,8 @@
       <c r="F22" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
     </row>
     <row r="23" spans="3:8" ht="18" x14ac:dyDescent="0.35">
       <c r="C23" s="2"/>
@@ -817,6 +817,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="G20:H20"/>
     <mergeCell ref="C1:G1"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="B5:G5"/>
@@ -824,13 +831,6 @@
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="F7:G7"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="G20:H20"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.19685039370078741" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -857,52 +857,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="3" spans="2:8" ht="18" x14ac:dyDescent="0.35">
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="20"/>
+      <c r="G3" s="14"/>
     </row>
     <row r="5" spans="2:8" ht="141.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
+      <c r="B5" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
     </row>
     <row r="7" spans="2:8" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22" t="s">
+      <c r="E7" s="16"/>
+      <c r="F7" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="22"/>
+      <c r="G7" s="16"/>
     </row>
     <row r="8" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
       <c r="D8" s="3" t="s">
         <v>4</v>
       </c>
@@ -947,38 +947,38 @@
       <c r="G10" s="7"/>
     </row>
     <row r="12" spans="2:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C12" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
+      <c r="C12" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
     </row>
     <row r="14" spans="2:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C14" s="15" t="str">
+      <c r="C14" s="19" t="str">
         <f>+D7</f>
         <v>""NAM PAXTA TEKS GALLA" MCHJ"</v>
       </c>
-      <c r="D14" s="15"/>
+      <c r="D14" s="19"/>
       <c r="E14" s="8"/>
-      <c r="F14" s="16" t="str">
+      <c r="F14" s="20" t="str">
         <f>+F7</f>
         <v>"OROL NIHOLLARI" FX</v>
       </c>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
     </row>
     <row r="15" spans="2:8" ht="59.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="17"/>
+      <c r="D15" s="21"/>
       <c r="E15" s="8"/>
-      <c r="F15" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="G15" s="18"/>
+      <c r="F15" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="22"/>
       <c r="H15" s="9"/>
     </row>
     <row r="16" spans="2:8" ht="21" x14ac:dyDescent="0.4">
@@ -1040,10 +1040,10 @@
       <c r="F20" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="G20" s="13" t="s">
+      <c r="G20" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="H20" s="13"/>
+      <c r="H20" s="17"/>
     </row>
     <row r="21" spans="3:8" ht="21" x14ac:dyDescent="0.4">
       <c r="C21" s="8"/>
@@ -1062,8 +1062,8 @@
       <c r="F22" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
     </row>
     <row r="23" spans="3:8" ht="18" x14ac:dyDescent="0.35">
       <c r="C23" s="2"/>
@@ -1074,6 +1074,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
     <mergeCell ref="G22:H22"/>
     <mergeCell ref="C12:G12"/>
     <mergeCell ref="C14:D14"/>
@@ -1081,13 +1088,6 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="F15:G15"/>
     <mergeCell ref="G20:H20"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:G7"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.19685039370078741" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
